--- a/test-workflow-no-docker/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/test-workflow-no-docker/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:32:33+00:00</t>
+    <t>2026-06-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/test-workflow-no-docker/ig/ValueSet-as-vs-organization-types.xlsx
+++ b/test-workflow-no-docker/ig/ValueSet-as-vs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T11:33:59+00:00</t>
+    <t>2026-06-25T12:00:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
